--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714352C3-FCE6-461F-ABB0-98DBB8D2CFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE26600-CE30-41EE-8E07-57CE0081AC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -519,6 +519,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -565,6 +568,9 @@
                   <c:v>3.6779999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>3.9</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>3.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -651,6 +657,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -698,6 +707,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.5249999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -783,6 +795,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -830,6 +845,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>17.75</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>19.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -915,6 +933,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -962,6 +983,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>9.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10.433</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1269,6 +1293,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1316,6 +1343,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>20.972000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>20.59</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1401,6 +1431,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1447,6 +1480,9 @@
                   <c:v>10.492000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>10.476000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>10.476000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -1533,6 +1569,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1579,6 +1618,9 @@
                   <c:v>6.6</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>6.58</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>6.58</c:v>
                 </c:pt>
               </c:numCache>
@@ -1887,6 +1929,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1934,6 +1979,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>3.3250000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2019,6 +2067,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2066,6 +2117,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>6.0250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2151,6 +2205,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2198,6 +2255,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>8.9499999999999993</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2283,6 +2343,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2330,6 +2393,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>17.55</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16.649999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4594,7 +4660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -5381,6 +5447,56 @@
       </c>
       <c r="P15" s="9">
         <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A16" s="11">
+        <v>46139</v>
+      </c>
+      <c r="B16" s="11">
+        <v>46146</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="F16" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="G16" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="H16" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="I16" s="9">
+        <v>3</v>
+      </c>
+      <c r="J16" s="9">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="K16" s="9">
+        <v>28</v>
+      </c>
+      <c r="L16" s="9">
+        <v>15</v>
+      </c>
+      <c r="M16" s="9">
+        <v>19.25</v>
+      </c>
+      <c r="N16" s="9">
+        <v>12</v>
+      </c>
+      <c r="O16" s="9">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="P16" s="9">
+        <v>10.433</v>
       </c>
     </row>
   </sheetData>
@@ -5398,7 +5514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -5646,6 +5762,47 @@
       </c>
       <c r="M5" s="9">
         <v>7.2080000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B6" s="11">
+        <v>46142</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.375</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="9">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="F6" s="9">
+        <v>17.45</v>
+      </c>
+      <c r="G6" s="9">
+        <v>17.725000000000001</v>
+      </c>
+      <c r="H6" s="9">
+        <v>12.95</v>
+      </c>
+      <c r="I6" s="9">
+        <v>12.5</v>
+      </c>
+      <c r="J6" s="9">
+        <v>12.712999999999999</v>
+      </c>
+      <c r="K6" s="9">
+        <v>10.7</v>
+      </c>
+      <c r="L6" s="9">
+        <v>10.15</v>
+      </c>
+      <c r="M6" s="9">
+        <v>10.45</v>
       </c>
     </row>
   </sheetData>
@@ -5662,7 +5819,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -6325,6 +6482,47 @@
         <v>4.8</v>
       </c>
       <c r="M15" s="9">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A16" s="11">
+        <v>46139</v>
+      </c>
+      <c r="B16" s="11">
+        <v>46146</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="9">
+        <v>21.5</v>
+      </c>
+      <c r="F16" s="9">
+        <v>16</v>
+      </c>
+      <c r="G16" s="9">
+        <v>20.59</v>
+      </c>
+      <c r="H16" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="I16" s="9">
+        <v>8</v>
+      </c>
+      <c r="J16" s="9">
+        <v>10.476000000000001</v>
+      </c>
+      <c r="K16" s="9">
+        <v>9</v>
+      </c>
+      <c r="L16" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="M16" s="9">
         <v>6.58</v>
       </c>
     </row>
@@ -6342,7 +6540,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -7131,6 +7329,56 @@
       </c>
       <c r="P15" s="9">
         <v>17.55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A16" s="11">
+        <v>46139</v>
+      </c>
+      <c r="B16" s="11">
+        <v>46146</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="F16" s="9">
+        <v>2.98</v>
+      </c>
+      <c r="G16" s="9">
+        <v>3.19</v>
+      </c>
+      <c r="H16" s="9">
+        <v>6.2</v>
+      </c>
+      <c r="I16" s="9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J16" s="9">
+        <v>5.7</v>
+      </c>
+      <c r="K16" s="9">
+        <v>9.1</v>
+      </c>
+      <c r="L16" s="9">
+        <v>7.7</v>
+      </c>
+      <c r="M16" s="9">
+        <v>8.35</v>
+      </c>
+      <c r="N16" s="9">
+        <v>17.8</v>
+      </c>
+      <c r="O16" s="9">
+        <v>15.5</v>
+      </c>
+      <c r="P16" s="9">
+        <v>16.649999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -7382,7 +7630,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ9"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -7997,6 +8245,65 @@
       </c>
       <c r="V9" s="9">
         <v>154.97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A10" s="11">
+        <v>46142</v>
+      </c>
+      <c r="B10" s="11">
+        <v>46142</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.625</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="9">
+        <v>126.5</v>
+      </c>
+      <c r="F10" s="9">
+        <v>125.83</v>
+      </c>
+      <c r="G10" s="9">
+        <v>126.17</v>
+      </c>
+      <c r="H10" s="9">
+        <v>152.6</v>
+      </c>
+      <c r="I10" s="9">
+        <v>117.5</v>
+      </c>
+      <c r="J10" s="9">
+        <v>135</v>
+      </c>
+      <c r="K10" s="9">
+        <v>319.99</v>
+      </c>
+      <c r="L10" s="9">
+        <v>319.94</v>
+      </c>
+      <c r="M10" s="9">
+        <v>319.97000000000003</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="R10" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="S10" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="T10" s="9">
+        <v>162.79</v>
+      </c>
+      <c r="U10" s="9">
+        <v>154.97</v>
+      </c>
+      <c r="V10" s="9">
+        <v>158.88</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE26600-CE30-41EE-8E07-57CE0081AC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215FCBFB-884E-41B3-B8B4-655F02CE3240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -522,6 +522,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -572,6 +575,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>3.9</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -660,6 +666,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -710,6 +719,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>3.5249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.45</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -798,6 +810,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -848,6 +863,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>19.25</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>19.625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -936,6 +954,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -986,6 +1007,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>10.433</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>10.467000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1296,6 +1320,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1346,6 +1373,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>20.59</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20.472000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1434,6 +1464,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1483,6 +1516,9 @@
                   <c:v>10.476000000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>10.476000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>10.476000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -1572,6 +1608,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1621,6 +1660,9 @@
                   <c:v>6.58</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>6.58</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>6.58</c:v>
                 </c:pt>
               </c:numCache>
@@ -1932,6 +1974,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1982,6 +2027,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>3.19</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2070,6 +2118,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2120,6 +2171,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2208,6 +2262,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2258,6 +2315,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>8.35</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.1750000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2346,6 +2406,9 @@
                 <c:pt idx="13">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>46153</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2396,6 +2459,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>16.649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4660,7 +4726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -5497,6 +5563,56 @@
       </c>
       <c r="P16" s="9">
         <v>10.433</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
+        <v>46146</v>
+      </c>
+      <c r="B17" s="11">
+        <v>46153</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="F17" s="9">
+        <v>3</v>
+      </c>
+      <c r="G17" s="9">
+        <v>3.75</v>
+      </c>
+      <c r="H17" s="9">
+        <v>4</v>
+      </c>
+      <c r="I17" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="J17" s="9">
+        <v>3.45</v>
+      </c>
+      <c r="K17" s="9">
+        <v>30</v>
+      </c>
+      <c r="L17" s="9">
+        <v>15</v>
+      </c>
+      <c r="M17" s="9">
+        <v>19.625</v>
+      </c>
+      <c r="N17" s="9">
+        <v>12</v>
+      </c>
+      <c r="O17" s="9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="P17" s="9">
+        <v>10.467000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5819,7 +5935,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -6523,6 +6639,47 @@
         <v>4.8</v>
       </c>
       <c r="M16" s="9">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
+        <v>46146</v>
+      </c>
+      <c r="B17" s="11">
+        <v>46153</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="9">
+        <v>21.5</v>
+      </c>
+      <c r="F17" s="9">
+        <v>16</v>
+      </c>
+      <c r="G17" s="9">
+        <v>20.472000000000001</v>
+      </c>
+      <c r="H17" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="I17" s="9">
+        <v>8</v>
+      </c>
+      <c r="J17" s="9">
+        <v>10.476000000000001</v>
+      </c>
+      <c r="K17" s="9">
+        <v>9</v>
+      </c>
+      <c r="L17" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="M17" s="9">
         <v>6.58</v>
       </c>
     </row>
@@ -6540,7 +6697,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -7379,6 +7536,56 @@
       </c>
       <c r="P16" s="9">
         <v>16.649999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
+        <v>46146</v>
+      </c>
+      <c r="B17" s="11">
+        <v>46153</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="F17" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G17" s="9">
+        <v>3.15</v>
+      </c>
+      <c r="H17" s="9">
+        <v>6.1</v>
+      </c>
+      <c r="I17" s="9">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="J17" s="9">
+        <v>5.6</v>
+      </c>
+      <c r="K17" s="9">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="L17" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="M17" s="9">
+        <v>8.1750000000000007</v>
+      </c>
+      <c r="N17" s="9">
+        <v>17.2</v>
+      </c>
+      <c r="O17" s="9">
+        <v>15</v>
+      </c>
+      <c r="P17" s="9">
+        <v>16.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6255ED-9EA4-4B2D-A07D-83574D2F5C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FCCB4C-EB83-9549-9806-AE108BCEC16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11440" yWindow="600" windowWidth="21260" windowHeight="18380" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -4991,12 +4991,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -6095,12 +6095,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -6441,12 +6441,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -7367,14 +7367,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
   <dimension ref="A1:Y21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -8472,14 +8472,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -8744,15 +8744,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
   <dimension ref="A1:AJ12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="22" width="10.453125" style="9" customWidth="1"/>
-    <col min="23" max="24" width="13.08984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="14.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="22" width="10.5" style="9" customWidth="1"/>
+    <col min="23" max="24" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="28" max="36" width="9" style="9"/>
     <col min="37" max="16384" width="9" style="5"/>
   </cols>
@@ -9552,7 +9552,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9564,11 +9564,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FCCB4C-EB83-9549-9806-AE108BCEC16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF34F94F-3C62-4917-BC25-B6C4B1C6FA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11440" yWindow="600" windowWidth="21260" windowHeight="18380" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="74">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -304,7 +304,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -345,6 +345,14 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -369,7 +377,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -407,10 +415,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -428,7 +466,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -537,6 +575,9 @@
                 <c:pt idx="18">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -602,6 +643,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>3.8250000000000002</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -705,6 +749,9 @@
                 <c:pt idx="18">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -770,6 +817,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>3.5129999999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.5630000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -873,6 +923,9 @@
                 <c:pt idx="18">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -938,6 +991,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>24.318000000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>26.545000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1041,6 +1097,9 @@
                 <c:pt idx="18">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1106,6 +1165,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>12.233000000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>13.266999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1322,7 +1384,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1431,6 +1493,9 @@
                 <c:pt idx="18">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1496,6 +1561,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>20.683</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20.638000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1599,6 +1667,9 @@
                 <c:pt idx="18">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1663,6 +1734,9 @@
                   <c:v>10.476000000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>10.48</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>10.48</c:v>
                 </c:pt>
               </c:numCache>
@@ -1767,6 +1841,9 @@
                 <c:pt idx="18">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1831,6 +1908,9 @@
                   <c:v>6.58</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>6.58</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>6.58</c:v>
                 </c:pt>
               </c:numCache>
@@ -2048,7 +2128,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2157,6 +2237,9 @@
                 <c:pt idx="18">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2222,6 +2305,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>2.9750000000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2325,6 +2411,9 @@
                 <c:pt idx="18">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2390,6 +2479,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>4.9249999999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2493,6 +2585,9 @@
                 <c:pt idx="18">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2558,6 +2653,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>7.375</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2661,6 +2759,9 @@
                 <c:pt idx="18">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="19">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2726,6 +2827,9 @@
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>14.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4990,1093 +5094,1143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:Y22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="25" width="9" style="9"/>
-    <col min="26" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="25" width="9" style="26"/>
+    <col min="26" max="16384" width="9" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:25" s="20" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="4" t="s">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="11">
+      <c r="A3" s="23">
         <v>46034</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="23">
         <v>46048</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="21">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="21">
         <v>1.5</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="21">
         <v>1.722</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="21">
         <v>2.0499999999999998</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="21">
         <v>1.3</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="21">
         <v>1.43</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="21">
         <v>7.45</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="21">
         <v>6.8</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="21">
         <v>7.1630000000000003</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="21">
         <v>6</v>
       </c>
-      <c r="O3" s="4">
+      <c r="O3" s="21">
         <v>4.05</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="21">
         <v>4.4050000000000002</v>
       </c>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="11">
+      <c r="A4" s="23">
         <v>46048</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="23">
         <v>46055</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="21">
         <v>2.4</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="21">
         <v>1.7</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="21">
         <v>1.9670000000000001</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="21">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="21">
         <v>1.5</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="21">
         <v>1.623</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="21">
         <v>8</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="21">
         <v>7.4</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="21">
         <v>7.7</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="21">
         <v>6.2</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="21">
         <v>4.3499999999999996</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="21">
         <v>4.9050000000000002</v>
       </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="11">
+      <c r="A5" s="23">
         <v>46055</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="23">
         <v>46062</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="26">
         <v>2.5</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="26">
         <v>1.75</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="26">
         <v>2.028</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="26">
         <v>2.25</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="26">
         <v>1.55</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="26">
         <v>1.673</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="26">
         <v>8.1999999999999993</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="26">
         <v>7.5</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="26">
         <v>7.9</v>
       </c>
-      <c r="N5" s="9">
+      <c r="N5" s="26">
         <v>6.25</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="26">
         <v>4.4000000000000004</v>
       </c>
-      <c r="P5" s="9">
+      <c r="P5" s="26">
         <v>4.9729999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="11">
+      <c r="A6" s="23">
         <v>46062</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="23">
         <v>46076</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="26">
         <v>2.6</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="26">
         <v>1.85</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="26">
         <v>2.1</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="26">
         <v>2.35</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="26">
         <v>1.6</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="26">
         <v>1.7490000000000001</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="26">
         <v>10</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="26">
         <v>7.8</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="26">
         <v>8.375</v>
       </c>
-      <c r="N6" s="9">
+      <c r="N6" s="26">
         <v>6.5</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="26">
         <v>4.5</v>
       </c>
-      <c r="P6" s="9">
+      <c r="P6" s="26">
         <v>5.2450000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="11">
+      <c r="A7" s="23">
         <v>46076</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="23">
         <v>46083</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="26">
         <v>2.8</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="26">
         <v>1.9</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="26">
         <v>2.1890000000000001</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="26">
         <v>2.4</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="26">
         <v>1.65</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="26">
         <v>1.8180000000000001</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="26">
         <v>11</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="26">
         <v>8</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="26">
         <v>8.875</v>
       </c>
-      <c r="N7" s="9">
+      <c r="N7" s="26">
         <v>6.8</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="26">
         <v>4.5999999999999996</v>
       </c>
-      <c r="P7" s="9">
+      <c r="P7" s="26">
         <v>5.4820000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="11">
+      <c r="A8" s="23">
         <v>46083</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="23">
         <v>46090</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="26">
         <v>2.8</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="26">
         <v>1.95</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="26">
         <v>2.25</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="26">
         <v>2.5</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="26">
         <v>1.7</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="26">
         <v>1.8740000000000001</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="26">
         <v>12</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="26">
         <v>8.4</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="26">
         <v>9.35</v>
       </c>
-      <c r="N8" s="9">
+      <c r="N8" s="26">
         <v>7</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="26">
         <v>5</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P8" s="26">
         <v>5.8179999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="11">
+      <c r="A9" s="23">
         <v>46090</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="23">
         <v>46097</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="26">
         <v>3</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="26">
         <v>2</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="26">
         <v>2.4670000000000001</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="26">
         <v>2.6</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="26">
         <v>1.8</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="26">
         <v>2.0169999999999999</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="26">
         <v>14.5</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="26">
         <v>9</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="26">
         <v>10.275</v>
       </c>
-      <c r="N9" s="9">
+      <c r="N9" s="26">
         <v>7.3</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="26">
         <v>5.8</v>
       </c>
-      <c r="P9" s="9">
+      <c r="P9" s="26">
         <v>6.2910000000000004</v>
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="11">
+      <c r="A10" s="23">
         <v>46097</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="23">
         <v>46104</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="26">
         <v>3.3</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="26">
         <v>2.35</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="26">
         <v>2.7330000000000001</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="26">
         <v>2.9</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="26">
         <v>2</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="26">
         <v>2.2650000000000001</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="26">
         <v>15</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="26">
         <v>9.5</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="26">
         <v>11.5</v>
       </c>
-      <c r="N10" s="9">
+      <c r="N10" s="26">
         <v>8</v>
       </c>
-      <c r="O10" s="9">
+      <c r="O10" s="26">
         <v>6</v>
       </c>
-      <c r="P10" s="9">
+      <c r="P10" s="26">
         <v>6.9329999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="11">
+      <c r="A11" s="23">
         <v>46104</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="23">
         <v>46111</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="26">
         <v>3.6</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="26">
         <v>2.5</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="26">
         <v>2.9889999999999999</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="26">
         <v>3.05</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="26">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="26">
         <v>2.4580000000000002</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="26">
         <v>15</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="26">
         <v>9.5</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="26">
         <v>12.625</v>
       </c>
-      <c r="N11" s="9">
+      <c r="N11" s="26">
         <v>8.3000000000000007</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="26">
         <v>6.5</v>
       </c>
-      <c r="P11" s="9">
+      <c r="P11" s="26">
         <v>7.5</v>
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="11">
+      <c r="A12" s="23">
         <v>46111</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="23">
         <v>46118</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="26">
         <v>3.7</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="26">
         <v>2.6</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="26">
         <v>3.089</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="26">
         <v>3.2</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="26">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="26">
         <v>2.573</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="26">
         <v>16</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="26">
         <v>10</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="26">
         <v>13.125</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="26">
         <v>8.3000000000000007</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="26">
         <v>6.8</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="26">
         <v>7.7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="11">
+      <c r="A13" s="23">
         <v>46118</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="23">
         <v>46125</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="26">
         <v>4.2</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="26">
         <v>3</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="26">
         <v>3.411</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="26">
         <v>3.5</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="26">
         <v>2.5</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="26">
         <v>2.8650000000000002</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="26">
         <v>20</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="26">
         <v>12</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="26">
         <v>15</v>
       </c>
-      <c r="N13" s="9">
+      <c r="N13" s="26">
         <v>9.5</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="26">
         <v>8</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="26">
         <v>8.6669999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="11">
+      <c r="A14" s="23">
         <v>46125</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>46132</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="26">
         <v>4.2</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="26">
         <v>3.3</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="26">
         <v>3.6779999999999999</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="26">
         <v>4</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="26">
         <v>2.8</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="26">
         <v>3.125</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="26">
         <v>22</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="26">
         <v>12</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="26">
         <v>16.5</v>
       </c>
-      <c r="N14" s="9">
+      <c r="N14" s="26">
         <v>10</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="26">
         <v>8.8000000000000007</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P14" s="26">
         <v>9.3670000000000009</v>
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="11">
+      <c r="A15" s="23">
         <v>46132</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>46139</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="26">
         <v>4.3</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="26">
         <v>3.5</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="26">
         <v>3.9</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="26">
         <v>4</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="26">
         <v>3</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="26">
         <v>3.4</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="26">
         <v>25</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="26">
         <v>14</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="26">
         <v>17.75</v>
       </c>
-      <c r="N15" s="9">
+      <c r="N15" s="26">
         <v>12</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="26">
         <v>9.1999999999999993</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P15" s="26">
         <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="11">
+      <c r="A16" s="23">
         <v>46139</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>46146</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="26">
         <v>4.5</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="26">
         <v>3.5</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="26">
         <v>3.9</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="26">
         <v>4.0999999999999996</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="26">
         <v>3</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="26">
         <v>3.5249999999999999</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="26">
         <v>28</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="26">
         <v>15</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="26">
         <v>19.25</v>
       </c>
-      <c r="N16" s="9">
+      <c r="N16" s="26">
         <v>12</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="26">
         <v>9.6999999999999993</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="26">
         <v>10.433</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="11">
+      <c r="A17" s="23">
         <v>46146</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="23">
         <v>46153</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="26">
         <v>4.5</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="26">
         <v>3</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="26">
         <v>3.75</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="26">
         <v>4</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="26">
         <v>2.9</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="26">
         <v>3.45</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="26">
         <v>30</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="26">
         <v>15</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="26">
         <v>19.625</v>
       </c>
-      <c r="N17" s="9">
+      <c r="N17" s="26">
         <v>12</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="26">
         <v>9.8000000000000007</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="26">
         <v>10.467000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="11">
+      <c r="A18" s="23">
         <v>46153</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="23">
         <v>46160</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="26">
         <v>4.5</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="26">
         <v>3</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="26">
         <v>3.7250000000000001</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="26">
         <v>3.8</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="26">
         <v>3</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="26">
         <v>3.4249999999999998</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="26">
         <v>32</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="26">
         <v>16</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M18" s="26">
         <v>20.295000000000002</v>
       </c>
-      <c r="N18" s="9">
+      <c r="N18" s="26">
         <v>12.3</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="26">
         <v>10.199999999999999</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P18" s="26">
         <v>10.7</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="11">
+      <c r="A19" s="23">
         <v>46160</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="23">
         <v>46167</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="26">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="26">
         <v>3.1</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="26">
         <v>3.7749999999999999</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="26">
         <v>3.8</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="26">
         <v>3.2</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="26">
         <v>3.5</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="26">
         <v>34</v>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="26">
         <v>18</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M19" s="26">
         <v>21.681999999999999</v>
       </c>
-      <c r="N19" s="9">
+      <c r="N19" s="26">
         <v>12.5</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="26">
         <v>10.7</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P19" s="26">
         <v>11.266999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="11">
+      <c r="A20" s="23">
         <v>46167</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="23">
         <v>46174</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="26">
         <v>4.4000000000000004</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="26">
         <v>3.3</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="26">
         <v>3.7949999999999999</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="26">
         <v>3.8</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="26">
         <v>3.3</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="26">
         <v>3.5</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="26">
         <v>35</v>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="26">
         <v>18</v>
       </c>
-      <c r="M20" s="9">
+      <c r="M20" s="26">
         <v>22.181999999999999</v>
       </c>
-      <c r="N20" s="9">
+      <c r="N20" s="26">
         <v>12.5</v>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="26">
         <v>10.7</v>
       </c>
-      <c r="P20" s="9">
+      <c r="P20" s="26">
         <v>11.5</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="11">
+      <c r="A21" s="23">
         <v>46174</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="23">
         <v>46181</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="26">
         <v>4.5</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="26">
         <v>3.45</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="26">
         <v>3.8250000000000002</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="26">
         <v>3.8</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="26">
         <v>3.3</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="26">
         <v>3.5129999999999999</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="26">
         <v>40</v>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="26">
         <v>20</v>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="26">
         <v>24.318000000000001</v>
       </c>
-      <c r="N21" s="9">
+      <c r="N21" s="26">
         <v>14</v>
       </c>
-      <c r="O21" s="9">
+      <c r="O21" s="26">
         <v>11</v>
       </c>
-      <c r="P21" s="9">
+      <c r="P21" s="26">
         <v>12.233000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="23">
+        <v>46181</v>
+      </c>
+      <c r="B22" s="23">
+        <v>46188</v>
+      </c>
+      <c r="C22" s="24">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="26">
+        <v>4.5</v>
+      </c>
+      <c r="F22" s="26">
+        <v>3.6</v>
+      </c>
+      <c r="G22" s="26">
+        <v>3.9</v>
+      </c>
+      <c r="H22" s="26">
+        <v>3.85</v>
+      </c>
+      <c r="I22" s="26">
+        <v>3.35</v>
+      </c>
+      <c r="J22" s="26">
+        <v>3.5630000000000002</v>
+      </c>
+      <c r="K22" s="26">
+        <v>40</v>
+      </c>
+      <c r="L22" s="26">
+        <v>22</v>
+      </c>
+      <c r="M22" s="26">
+        <v>26.545000000000002</v>
+      </c>
+      <c r="N22" s="26">
+        <v>15</v>
+      </c>
+      <c r="O22" s="26">
+        <v>12</v>
+      </c>
+      <c r="P22" s="26">
+        <v>13.266999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6095,334 +6249,334 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="25" width="9" style="9"/>
-    <col min="26" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="25" width="9" style="26"/>
+    <col min="26" max="16384" width="9" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:25" s="20" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="4" t="s">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="11">
+      <c r="A3" s="23">
         <v>46022</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="23">
         <v>46052</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="24">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4">
+      <c r="E3" s="21"/>
+      <c r="F3" s="21">
         <v>3.22</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="21">
         <v>3.3260000000000001</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4">
+      <c r="H3" s="21"/>
+      <c r="I3" s="21">
         <v>2.6</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="21">
         <v>3.3</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4">
+      <c r="K3" s="21"/>
+      <c r="L3" s="21">
         <v>2.33</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="21">
         <v>2.6629999999999998</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="11">
+      <c r="A4" s="23">
         <v>46052</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="23">
         <v>46079</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="24">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="21">
         <v>9.6999999999999993</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="21">
         <v>9.25</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="21">
         <v>9.4580000000000002</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="21">
         <v>7.2</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="21">
         <v>6.9</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="21">
         <v>7.0229999999999997</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="21">
         <v>6.15</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="21">
         <v>5.2</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="21">
         <v>5.57</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="11">
+      <c r="A5" s="23">
         <v>46079</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="23">
         <v>46112</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="24">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="26">
         <v>12.75</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="26">
         <v>12.55</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="26">
         <v>12.664999999999999</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="26">
         <v>8.6</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="26">
         <v>8.4</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="26">
         <v>8.5129999999999999</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="26">
         <v>7.3</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="26">
         <v>6.9</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="26">
         <v>7.2080000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="11">
+      <c r="A6" s="23">
         <v>46112</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="23">
         <v>46142</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="24">
         <v>0.375</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="26">
         <v>17.899999999999999</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="26">
         <v>17.45</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="26">
         <v>17.725000000000001</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="26">
         <v>12.95</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="26">
         <v>12.5</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="26">
         <v>12.712999999999999</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="26">
         <v>10.7</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="26">
         <v>10.15</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="26">
         <v>10.45</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="11">
+      <c r="A7" s="23">
         <v>46142</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="23">
         <v>46171</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="24">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="26">
         <v>24.3</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="26">
         <v>23.85</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="26">
         <v>24.158000000000001</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="26">
         <v>17.5</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="26">
         <v>17.149999999999999</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="26">
         <v>17.324999999999999</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="26">
         <v>14.2</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="26">
         <v>13.7</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="26">
         <v>14.1</v>
       </c>
     </row>
@@ -6440,915 +6594,956 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:Y22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="25" width="9" style="9"/>
-    <col min="26" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="25" width="9" style="26"/>
+    <col min="26" max="16384" width="9" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:25" s="20" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="4" t="s">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="11">
+      <c r="A3" s="23">
         <v>46034</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="23">
         <v>46048</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="21">
         <v>15.8</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="21">
         <v>14</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="21">
         <v>15.052</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="21">
         <v>8</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="21">
         <v>6</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="21">
         <v>6.968</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="21">
         <v>6</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="21">
         <v>4</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="21">
         <v>4.9870000000000001</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="11">
+      <c r="A4" s="23">
         <v>46048</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="23">
         <v>46055</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="21">
         <v>17.5</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="21">
         <v>14.5</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="21">
         <v>16.309999999999999</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="21">
         <v>8.5</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="21">
         <v>7</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="21">
         <v>7.5720000000000001</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="21">
         <v>6</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="21">
         <v>4</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="21">
         <v>4.9870000000000001</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="11">
+      <c r="A5" s="23">
         <v>46055</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="23">
         <v>46062</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="26">
         <v>19.5</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="26">
         <v>15.5</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="26">
         <v>17.724</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="26">
         <v>10.5</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="26">
         <v>7.5</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="26">
         <v>8.7479999999999993</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="26">
         <v>7.5</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="26">
         <v>4.5</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="26">
         <v>5.5170000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="11">
+      <c r="A6" s="23">
         <v>46062</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="23">
         <v>46076</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="26">
         <v>20</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="26">
         <v>15.5</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="26">
         <v>17.948</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="26">
         <v>10.5</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="26">
         <v>7.5</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="26">
         <v>8.7479999999999993</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="26">
         <v>7.5</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="26">
         <v>4.5</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="26">
         <v>5.5170000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="11">
+      <c r="A7" s="23">
         <v>46076</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="23">
         <v>46083</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="26">
         <v>20</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="26">
         <v>15.5</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="26">
         <v>17.948</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="26">
         <v>10.5</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="26">
         <v>7.5</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="26">
         <v>8.7479999999999993</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="26">
         <v>7.5</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="26">
         <v>4.5</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="26">
         <v>5.5170000000000003</v>
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="11">
+      <c r="A8" s="23">
         <v>46083</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="23">
         <v>46090</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="26">
         <v>22</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="26">
         <v>17</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="26">
         <v>20.585999999999999</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="26">
         <v>11</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="26">
         <v>8</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="26">
         <v>10.14</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="26">
         <v>9.5</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="26">
         <v>5</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="26">
         <v>6.45</v>
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="11">
+      <c r="A9" s="23">
         <v>46090</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="23">
         <v>46097</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="26">
         <v>25</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="26">
         <v>18</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="26">
         <v>23.134</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="26">
         <v>12</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="26">
         <v>8.5</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="26">
         <v>11.24</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="26">
         <v>9.8000000000000007</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="26">
         <v>5</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="26">
         <v>6.9669999999999996</v>
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="11">
+      <c r="A10" s="23">
         <v>46097</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="23">
         <v>46104</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="26">
         <v>25</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="26">
         <v>18.5</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="26">
         <v>23</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="26">
         <v>12</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="26">
         <v>8.5</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="26">
         <v>11.24</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="26">
         <v>9.8000000000000007</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="26">
         <v>5</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="26">
         <v>6.9669999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="11">
+      <c r="A11" s="23">
         <v>46104</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="23">
         <v>46111</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="26">
         <v>25</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="26">
         <v>18.5</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="26">
         <v>22.834</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="26">
         <v>12</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="26">
         <v>8.5</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="26">
         <v>11.24</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="26">
         <v>9.8000000000000007</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="26">
         <v>5</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="26">
         <v>6.9669999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="11">
+      <c r="A12" s="23">
         <v>46111</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="23">
         <v>46118</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="26">
         <v>24</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="26">
         <v>17</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="26">
         <v>22.155000000000001</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="26">
         <v>11.8</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="26">
         <v>8</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="26">
         <v>10.92</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="26">
         <v>9.5</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="26">
         <v>5</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="26">
         <v>6.8330000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="11">
+      <c r="A13" s="23">
         <v>46118</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="23">
         <v>46125</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="26">
         <v>23.5</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="26">
         <v>17</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="26">
         <v>21.678999999999998</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="26">
         <v>11.8</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="26">
         <v>8</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="26">
         <v>10.92</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="26">
         <v>9.5</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="26">
         <v>5</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="26">
         <v>6.8330000000000002</v>
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="11">
+      <c r="A14" s="23">
         <v>46125</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>46132</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="26">
         <v>22</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="26">
         <v>16.5</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="26">
         <v>21</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="26">
         <v>11.5</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="26">
         <v>8</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="26">
         <v>10.492000000000001</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="26">
         <v>9</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="26">
         <v>4.8</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="26">
         <v>6.6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="11">
+      <c r="A15" s="23">
         <v>46132</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>46139</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="26">
         <v>21.8</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="26">
         <v>16.5</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="26">
         <v>20.972000000000001</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="26">
         <v>11.5</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="26">
         <v>8</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="26">
         <v>10.476000000000001</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="26">
         <v>9</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="26">
         <v>4.8</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="26">
         <v>6.58</v>
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="11">
+      <c r="A16" s="23">
         <v>46139</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>46146</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="26">
         <v>21.5</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="26">
         <v>16</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="26">
         <v>20.59</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="26">
         <v>11.5</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="26">
         <v>8</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="26">
         <v>10.476000000000001</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="26">
         <v>9</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="26">
         <v>4.8</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="26">
         <v>6.58</v>
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="11">
+      <c r="A17" s="23">
         <v>46146</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="23">
         <v>46153</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="26">
         <v>21.5</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="26">
         <v>16</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="26">
         <v>20.472000000000001</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="26">
         <v>11.5</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="26">
         <v>8</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="26">
         <v>10.476000000000001</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="26">
         <v>9</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="26">
         <v>4.8</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="26">
         <v>6.58</v>
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="11">
+      <c r="A18" s="23">
         <v>46153</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="23">
         <v>46160</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="26">
         <v>21.5</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="26">
         <v>16</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="26">
         <v>20.541</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="26">
         <v>11.5</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="26">
         <v>8</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="26">
         <v>10.476000000000001</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="26">
         <v>9</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="26">
         <v>4.8</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M18" s="26">
         <v>6.58</v>
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="11">
+      <c r="A19" s="23">
         <v>46160</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="23">
         <v>46167</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="26">
         <v>22</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="26">
         <v>16</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="26">
         <v>20.707000000000001</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="26">
         <v>11.5</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="26">
         <v>8</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="26">
         <v>10.476000000000001</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="26">
         <v>9</v>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="26">
         <v>4.8</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M19" s="26">
         <v>6.58</v>
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="11">
+      <c r="A20" s="23">
         <v>46167</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="23">
         <v>46174</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="26">
         <v>22</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="26">
         <v>16</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="26">
         <v>20.638000000000002</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="26">
         <v>11.5</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="26">
         <v>8</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="26">
         <v>10.476000000000001</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="26">
         <v>9</v>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="26">
         <v>4.8</v>
       </c>
-      <c r="M20" s="9">
+      <c r="M20" s="26">
         <v>6.58</v>
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="11">
+      <c r="A21" s="23">
         <v>46174</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="23">
         <v>46181</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="26">
         <v>22.5</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="26">
         <v>16.5</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="26">
         <v>20.683</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="26">
         <v>11.5</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="26">
         <v>8.5</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="26">
         <v>10.48</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="26">
         <v>9</v>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="26">
         <v>4.8</v>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="26">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="23">
+        <v>46181</v>
+      </c>
+      <c r="B22" s="23">
+        <v>46188</v>
+      </c>
+      <c r="C22" s="24">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="26">
+        <v>22.5</v>
+      </c>
+      <c r="F22" s="26">
+        <v>16.5</v>
+      </c>
+      <c r="G22" s="26">
+        <v>20.638000000000002</v>
+      </c>
+      <c r="H22" s="26">
+        <v>11.5</v>
+      </c>
+      <c r="I22" s="26">
+        <v>8.5</v>
+      </c>
+      <c r="J22" s="26">
+        <v>10.48</v>
+      </c>
+      <c r="K22" s="26">
+        <v>9</v>
+      </c>
+      <c r="L22" s="26">
+        <v>4.8</v>
+      </c>
+      <c r="M22" s="26">
         <v>6.58</v>
       </c>
     </row>
@@ -7366,1095 +7561,1145 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:Y22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="25" width="9" style="9"/>
-    <col min="26" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="12.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="17" max="25" width="9" style="26"/>
+    <col min="26" max="16384" width="9" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="3" customFormat="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:25" s="20" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="4" t="s">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="11">
+      <c r="A3" s="23">
         <v>46034</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="23">
         <v>46048</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="21">
         <v>2.7</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="21">
         <v>2.1</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="21">
         <v>2.2149999999999999</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="21">
         <v>4.2</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="21">
         <v>3.6</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="21">
         <v>3.7250000000000001</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="21">
         <v>5.8</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="21">
         <v>4.8</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="21">
         <v>5.15</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3" s="21">
         <v>11</v>
       </c>
-      <c r="O3" s="4">
+      <c r="O3" s="21">
         <v>9.4</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="21">
         <v>9.6999999999999993</v>
       </c>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="11">
+      <c r="A4" s="23">
         <v>46048</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="23">
         <v>46055</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="21">
         <v>2.7</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="21">
         <v>2.15</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="21">
         <v>2.2400000000000002</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="21">
         <v>4.7</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="21">
         <v>3.9</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="21">
         <v>4.2850000000000001</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="21">
         <v>6.6</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="21">
         <v>5.7</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="21">
         <v>6</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="21">
         <v>13.5</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="21">
         <v>11.3</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="21">
         <v>11.8</v>
       </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="11">
+      <c r="A5" s="23">
         <v>46055</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="23">
         <v>46062</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="26">
         <v>2.8</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="26">
         <v>2.25</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="26">
         <v>2.35</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="26">
         <v>4.8</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="26">
         <v>4.3</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="26">
         <v>4.5</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="26">
         <v>6.95</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="26">
         <v>6.2</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="26">
         <v>6.4</v>
       </c>
-      <c r="N5" s="9">
+      <c r="N5" s="26">
         <v>14.5</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="26">
         <v>12.4</v>
       </c>
-      <c r="P5" s="9">
+      <c r="P5" s="26">
         <v>12.8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="11">
+      <c r="A6" s="23">
         <v>46062</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="23">
         <v>46076</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="26">
         <v>2.8</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="26">
         <v>2.25</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="26">
         <v>2.415</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="26">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="26">
         <v>4.3</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="26">
         <v>4.55</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="26">
         <v>7.1</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="26">
         <v>6.3</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="26">
         <v>6.55</v>
       </c>
-      <c r="N6" s="9">
+      <c r="N6" s="26">
         <v>14.6</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="26">
         <v>12.6</v>
       </c>
-      <c r="P6" s="9">
+      <c r="P6" s="26">
         <v>12.95</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="11">
+      <c r="A7" s="23">
         <v>46076</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="23">
         <v>46083</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="26">
         <v>2.8</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="26">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="26">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="26">
         <v>5</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="26">
         <v>4.5</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="26">
         <v>4.7</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="26">
         <v>7.2</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="26">
         <v>6.4</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="26">
         <v>7.6</v>
       </c>
-      <c r="N7" s="9">
+      <c r="N7" s="26">
         <v>14.9</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="26">
         <v>12.8</v>
       </c>
-      <c r="P7" s="9">
+      <c r="P7" s="26">
         <v>13.05</v>
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="11">
+      <c r="A8" s="23">
         <v>46083</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="23">
         <v>46090</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="26">
         <v>2.8</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="26">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="26">
         <v>2.4649999999999999</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="26">
         <v>5</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="26">
         <v>4.5</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="26">
         <v>4.75</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="26">
         <v>7.2</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="26">
         <v>6.4</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="26">
         <v>6.7249999999999996</v>
       </c>
-      <c r="N8" s="9">
+      <c r="N8" s="26">
         <v>14.9</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="26">
         <v>12.8</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P8" s="26">
         <v>13.05</v>
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="11">
+      <c r="A9" s="23">
         <v>46090</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="23">
         <v>46097</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="26">
         <v>3</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="26">
         <v>2.5</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="26">
         <v>2.7749999999999999</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="26">
         <v>5.7</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="26">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="26">
         <v>5.25</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="26">
         <v>8</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="26">
         <v>6.85</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="26">
         <v>7.55</v>
       </c>
-      <c r="N9" s="9">
+      <c r="N9" s="26">
         <v>16</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="26">
         <v>13.8</v>
       </c>
-      <c r="P9" s="9">
+      <c r="P9" s="26">
         <v>15.1</v>
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="11">
+      <c r="A10" s="23">
         <v>46097</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="23">
         <v>46104</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="26">
         <v>3.5</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="26">
         <v>2.9</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="26">
         <v>3.15</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="26">
         <v>6.5</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="26">
         <v>5.8</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="26">
         <v>6.1</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="26">
         <v>9.6</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="26">
         <v>8.6</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="26">
         <v>8.9499999999999993</v>
       </c>
-      <c r="N10" s="9">
+      <c r="N10" s="26">
         <v>19.8</v>
       </c>
-      <c r="O10" s="9">
+      <c r="O10" s="26">
         <v>17.2</v>
       </c>
-      <c r="P10" s="9">
+      <c r="P10" s="26">
         <v>17.95</v>
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="11">
+      <c r="A11" s="23">
         <v>46104</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="23">
         <v>46111</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="26">
         <v>3.8</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="26">
         <v>3</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="26">
         <v>3.35</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="26">
         <v>6.8</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="26">
         <v>6</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="26">
         <v>6.4</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="26">
         <v>10</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="26">
         <v>9</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="26">
         <v>9.375</v>
       </c>
-      <c r="N11" s="9">
+      <c r="N11" s="26">
         <v>19.8</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="26">
         <v>18.399999999999999</v>
       </c>
-      <c r="P11" s="9">
+      <c r="P11" s="26">
         <v>18.95</v>
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="11">
+      <c r="A12" s="23">
         <v>46111</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="23">
         <v>46118</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="26">
         <v>3.8</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="26">
         <v>3.1</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="26">
         <v>3.3450000000000002</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="26">
         <v>6.8</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="26">
         <v>6</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="26">
         <v>6.35</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="26">
         <v>10</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="26">
         <v>9</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="26">
         <v>9.3000000000000007</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="26">
         <v>19.3</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="26">
         <v>17.8</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="26">
         <v>18.600000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="11">
+      <c r="A13" s="23">
         <v>46118</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="23">
         <v>46125</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="26">
         <v>3.8</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="26">
         <v>3.1</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="26">
         <v>3.34</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="26">
         <v>6.8</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="26">
         <v>6</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="26">
         <v>6.3250000000000002</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="26">
         <v>10</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="26">
         <v>9</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="26">
         <v>9.2750000000000004</v>
       </c>
-      <c r="N13" s="9">
+      <c r="N13" s="26">
         <v>19.3</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="26">
         <v>17.8</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="26">
         <v>18.55</v>
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="11">
+      <c r="A14" s="23">
         <v>46125</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="23">
         <v>46132</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="26">
         <v>3.8</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="26">
         <v>3.1</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="26">
         <v>3.34</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="26">
         <v>6.7</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="26">
         <v>5.7</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="26">
         <v>6.2</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="26">
         <v>9.8000000000000007</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="26">
         <v>8.6999999999999993</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="26">
         <v>9.1750000000000007</v>
       </c>
-      <c r="N14" s="9">
+      <c r="N14" s="26">
         <v>19</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="26">
         <v>17</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P14" s="26">
         <v>18.25</v>
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="11">
+      <c r="A15" s="23">
         <v>46132</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="23">
         <v>46139</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="26">
         <v>3.7</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="26">
         <v>3.1</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="26">
         <v>3.3250000000000002</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="26">
         <v>6.4</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="26">
         <v>5.4</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="26">
         <v>6.0250000000000004</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="26">
         <v>9.5</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="26">
         <v>8.4</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="26">
         <v>8.9499999999999993</v>
       </c>
-      <c r="N15" s="9">
+      <c r="N15" s="26">
         <v>18.5</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="26">
         <v>16.2</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P15" s="26">
         <v>17.55</v>
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="11">
+      <c r="A16" s="23">
         <v>46139</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="23">
         <v>46146</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="26">
         <v>3.6</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="26">
         <v>2.98</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="26">
         <v>3.19</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="26">
         <v>6.2</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="26">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="26">
         <v>5.7</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="26">
         <v>9.1</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="26">
         <v>7.7</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="26">
         <v>8.35</v>
       </c>
-      <c r="N16" s="9">
+      <c r="N16" s="26">
         <v>17.8</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="26">
         <v>15.5</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="26">
         <v>16.649999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="11">
+      <c r="A17" s="23">
         <v>46146</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="23">
         <v>46153</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="26">
         <v>3.6</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="26">
         <v>2.9</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="26">
         <v>3.15</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="26">
         <v>6.1</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="26">
         <v>4.8499999999999996</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="26">
         <v>5.6</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="26">
         <v>8.8000000000000007</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="26">
         <v>7.5</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="26">
         <v>8.1750000000000007</v>
       </c>
-      <c r="N17" s="9">
+      <c r="N17" s="26">
         <v>17.2</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="26">
         <v>15</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="26">
         <v>16.2</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="11">
+      <c r="A18" s="23">
         <v>46153</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="23">
         <v>46160</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="26">
         <v>3.5</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="26">
         <v>2.8</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="26">
         <v>3.1</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="26">
         <v>6.1</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="26">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="26">
         <v>5.4</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="26">
         <v>8.6</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="26">
         <v>7</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M18" s="26">
         <v>8</v>
       </c>
-      <c r="N18" s="9">
+      <c r="N18" s="26">
         <v>16.8</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="26">
         <v>14.5</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P18" s="26">
         <v>15.85</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="11">
+      <c r="A19" s="23">
         <v>46160</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="23">
         <v>46167</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="26">
         <v>3.3</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="26">
         <v>2.75</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="26">
         <v>3.05</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="26">
         <v>5.8</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="26">
         <v>4.3</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="26">
         <v>5.1749999999999998</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="26">
         <v>8.4</v>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="26">
         <v>6.7</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M19" s="26">
         <v>7.65</v>
       </c>
-      <c r="N19" s="9">
+      <c r="N19" s="26">
         <v>16.2</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="26">
         <v>13.5</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P19" s="26">
         <v>15.35</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="11">
+      <c r="A20" s="23">
         <v>46167</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="23">
         <v>46174</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="26">
         <v>3.25</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="26">
         <v>2.7</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="26">
         <v>3</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="26">
         <v>5.5</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="26">
         <v>4.2</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="26">
         <v>4.9749999999999996</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="26">
         <v>8.1999999999999993</v>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="26">
         <v>6.5</v>
       </c>
-      <c r="M20" s="9">
+      <c r="M20" s="26">
         <v>7.4249999999999998</v>
       </c>
-      <c r="N20" s="9">
+      <c r="N20" s="26">
         <v>15.4</v>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="26">
         <v>13.5</v>
       </c>
-      <c r="P20" s="9">
+      <c r="P20" s="26">
         <v>14.75</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="11">
+      <c r="A21" s="23">
         <v>46174</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="23">
         <v>46181</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="24">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="26">
         <v>3.25</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="26">
         <v>2.7</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="26">
         <v>2.9750000000000001</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="26">
         <v>5.5</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="26">
         <v>4.2</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="26">
         <v>4.9249999999999998</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="26">
         <v>8</v>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="26">
         <v>6.5</v>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="26">
         <v>7.375</v>
       </c>
-      <c r="N21" s="9">
+      <c r="N21" s="26">
         <v>15.2</v>
       </c>
-      <c r="O21" s="9">
+      <c r="O21" s="26">
         <v>13.5</v>
       </c>
-      <c r="P21" s="9">
+      <c r="P21" s="26">
         <v>14.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="23">
+        <v>46181</v>
+      </c>
+      <c r="B22" s="23">
+        <v>46188</v>
+      </c>
+      <c r="C22" s="24">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="26">
+        <v>3.25</v>
+      </c>
+      <c r="F22" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="G22" s="26">
+        <v>2.95</v>
+      </c>
+      <c r="H22" s="26">
+        <v>5.3</v>
+      </c>
+      <c r="I22" s="26">
+        <v>4</v>
+      </c>
+      <c r="J22" s="26">
+        <v>4.75</v>
+      </c>
+      <c r="K22" s="26">
+        <v>7.9</v>
+      </c>
+      <c r="L22" s="26">
+        <v>6.5</v>
+      </c>
+      <c r="M22" s="26">
+        <v>7.15</v>
+      </c>
+      <c r="N22" s="26">
+        <v>15</v>
+      </c>
+      <c r="O22" s="26">
+        <v>13</v>
+      </c>
+      <c r="P22" s="26">
+        <v>14.2</v>
       </c>
     </row>
   </sheetData>
@@ -8472,14 +8717,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -8743,16 +8988,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:AJ13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="22" width="10.5" style="9" customWidth="1"/>
-    <col min="23" max="24" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="22" width="10.44140625" style="9" customWidth="1"/>
+    <col min="23" max="24" width="13.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="14.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="28" max="36" width="9" style="9"/>
     <col min="37" max="16384" width="9" style="5"/>
   </cols>
@@ -9535,6 +9780,65 @@
       </c>
       <c r="V12" s="9">
         <v>174.79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36">
+      <c r="A13" s="11">
+        <v>46185</v>
+      </c>
+      <c r="B13" s="11">
+        <v>46185</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0.625</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="9">
+        <v>242</v>
+      </c>
+      <c r="F13" s="9">
+        <v>242</v>
+      </c>
+      <c r="G13" s="9">
+        <v>242</v>
+      </c>
+      <c r="H13" s="9">
+        <v>130.30000000000001</v>
+      </c>
+      <c r="I13" s="9">
+        <v>115.7</v>
+      </c>
+      <c r="J13" s="9">
+        <v>133</v>
+      </c>
+      <c r="K13" s="9">
+        <v>249.99</v>
+      </c>
+      <c r="L13" s="9">
+        <v>249.99</v>
+      </c>
+      <c r="M13" s="9">
+        <v>249.99</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="R13" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="S13" s="9">
+        <v>399.99</v>
+      </c>
+      <c r="T13" s="9">
+        <v>170.97</v>
+      </c>
+      <c r="U13" s="9">
+        <v>164.97</v>
+      </c>
+      <c r="V13" s="9">
+        <v>167.97</v>
       </c>
     </row>
   </sheetData>
@@ -9552,7 +9856,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9564,11 +9868,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/data/industry/TrendForce/NAND Flash.xlsx
+++ b/data/industry/TrendForce/NAND Flash.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F88DF9-4EA8-E749-85B8-68220BFCCD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F24B0A-FFFD-4A97-8C34-E373D3999FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25660" yWindow="600" windowWidth="25540" windowHeight="25900" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="76">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -383,7 +383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -450,16 +450,10 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -477,7 +471,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -595,6 +589,9 @@
                 <c:pt idx="21">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -669,6 +666,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>3.9129999999999998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -781,6 +781,9 @@
                 <c:pt idx="21">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -855,6 +858,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>3.5779999999999998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.5979999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -967,6 +973,9 @@
                 <c:pt idx="21">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1041,6 +1050,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>28.181999999999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>29.068000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1153,6 +1165,9 @@
                 <c:pt idx="21">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="22">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1227,6 +1242,9 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>14.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1443,7 +1461,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1591,6 +1609,9 @@
                 <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1695,6 +1716,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>20.431000000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>20.068999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1837,6 +1861,9 @@
                 <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1941,6 +1968,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>10.372</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>10.18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2083,6 +2113,9 @@
                 <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2187,6 +2220,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>6.55</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6.4870000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2403,7 +2439,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2551,6 +2587,9 @@
                 <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2655,6 +2694,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>2.9249999999999998</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2797,6 +2839,9 @@
                 <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2901,6 +2946,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>4.5750000000000002</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4.5250000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3043,6 +3091,9 @@
                 <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3147,6 +3198,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3289,6 +3343,9 @@
                 <c:pt idx="31">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3393,6 +3450,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>13.55</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>13.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5657,13 +5717,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:Y35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="17" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="18"/>
   </cols>
   <sheetData>
@@ -7492,6 +7552,56 @@
       </c>
       <c r="P34" s="18">
         <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="15">
+        <v>46195</v>
+      </c>
+      <c r="B35" s="15">
+        <v>46202</v>
+      </c>
+      <c r="C35" s="16">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="18">
+        <v>4.5</v>
+      </c>
+      <c r="F35" s="18">
+        <v>3.52</v>
+      </c>
+      <c r="G35" s="18">
+        <v>3.92</v>
+      </c>
+      <c r="H35" s="18">
+        <v>3.85</v>
+      </c>
+      <c r="I35" s="18">
+        <v>3.32</v>
+      </c>
+      <c r="J35" s="18">
+        <v>3.5979999999999999</v>
+      </c>
+      <c r="K35" s="18">
+        <v>42</v>
+      </c>
+      <c r="L35" s="18">
+        <v>24</v>
+      </c>
+      <c r="M35" s="18">
+        <v>29.068000000000001</v>
+      </c>
+      <c r="N35" s="18">
+        <v>16</v>
+      </c>
+      <c r="O35" s="18">
+        <v>13.5</v>
+      </c>
+      <c r="P35" s="18">
+        <v>14.5</v>
       </c>
     </row>
   </sheetData>
@@ -7510,12 +7620,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6DA72B-EEC5-42C3-B327-5A9F9ACABB0A}">
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="17" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="18"/>
   </cols>
   <sheetData>
@@ -7854,13 +7964,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:Y35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="17" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="18"/>
   </cols>
   <sheetData>
@@ -9428,6 +9538,47 @@
       </c>
       <c r="M34" s="18">
         <v>6.55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="15">
+        <v>46195</v>
+      </c>
+      <c r="B35" s="15">
+        <v>46202</v>
+      </c>
+      <c r="C35" s="16">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="18">
+        <v>21.8</v>
+      </c>
+      <c r="F35" s="18">
+        <v>15.5</v>
+      </c>
+      <c r="G35" s="18">
+        <v>20.068999999999999</v>
+      </c>
+      <c r="H35" s="18">
+        <v>11.3</v>
+      </c>
+      <c r="I35" s="18">
+        <v>8</v>
+      </c>
+      <c r="J35" s="18">
+        <v>10.18</v>
+      </c>
+      <c r="K35" s="18">
+        <v>8.9</v>
+      </c>
+      <c r="L35" s="18">
+        <v>4.5</v>
+      </c>
+      <c r="M35" s="18">
+        <v>6.4870000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -9444,15 +9595,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:Y35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.1640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.1640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.109375" style="18" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="18"/>
   </cols>
   <sheetData>
@@ -11281,6 +11432,56 @@
       </c>
       <c r="P34" s="18">
         <v>13.55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="15">
+        <v>46195</v>
+      </c>
+      <c r="B35" s="15">
+        <v>46202</v>
+      </c>
+      <c r="C35" s="16">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="F35" s="18">
+        <v>2.7</v>
+      </c>
+      <c r="G35" s="18">
+        <v>2.9</v>
+      </c>
+      <c r="H35" s="18">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I35" s="18">
+        <v>3.9</v>
+      </c>
+      <c r="J35" s="18">
+        <v>4.5250000000000004</v>
+      </c>
+      <c r="K35" s="18">
+        <v>7.3</v>
+      </c>
+      <c r="L35" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="M35" s="18">
+        <v>6.75</v>
+      </c>
+      <c r="N35" s="18">
+        <v>14.2</v>
+      </c>
+      <c r="O35" s="18">
+        <v>12.2</v>
+      </c>
+      <c r="P35" s="18">
+        <v>13.4</v>
       </c>
     </row>
   </sheetData>
@@ -11298,14 +11499,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
   <dimension ref="A1:Y5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="13.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="25" width="9" style="9"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
@@ -11569,16 +11770,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:AJ19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="22" width="10.5" style="18" customWidth="1"/>
-    <col min="23" max="24" width="7.83203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.5" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="22" width="10.44140625" style="18" customWidth="1"/>
+    <col min="23" max="24" width="7.77734375" style="18" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.44140625" style="18" bestFit="1" customWidth="1"/>
     <col min="26" max="28" width="10.6640625" style="18" customWidth="1"/>
     <col min="29" max="36" width="9" style="18"/>
   </cols>
@@ -11764,13 +11965,13 @@
       <c r="AJ2" s="14"/>
     </row>
     <row r="3" spans="1:36">
-      <c r="A3" s="26">
+      <c r="A3" s="19">
         <v>45961</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="19">
         <v>45961</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="20">
         <v>0.60416666666666663</v>
       </c>
       <c r="D3" s="17" t="s">
@@ -11840,13 +12041,13 @@
       <c r="AJ3" s="14"/>
     </row>
     <row r="4" spans="1:36">
-      <c r="A4" s="26">
+      <c r="A4" s="19">
         <v>45975</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="19">
         <v>45975</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="20">
         <v>0.5625</v>
       </c>
       <c r="D4" s="17" t="s">
@@ -12818,6 +13019,65 @@
       </c>
       <c r="V18" s="18">
         <v>167.97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
+      <c r="A19" s="15">
+        <v>46199</v>
+      </c>
+      <c r="B19" s="15">
+        <v>46199</v>
+      </c>
+      <c r="C19" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="18">
+        <v>242</v>
+      </c>
+      <c r="F19" s="18">
+        <v>242</v>
+      </c>
+      <c r="G19" s="18">
+        <v>242</v>
+      </c>
+      <c r="H19" s="18">
+        <v>149.19999999999999</v>
+      </c>
+      <c r="I19" s="18">
+        <v>114.8</v>
+      </c>
+      <c r="J19" s="18">
+        <v>132</v>
+      </c>
+      <c r="K19" s="18">
+        <v>219.99</v>
+      </c>
+      <c r="L19" s="18">
+        <v>219.99</v>
+      </c>
+      <c r="M19" s="18">
+        <v>219.99</v>
+      </c>
+      <c r="Q19" s="18">
+        <v>399.99</v>
+      </c>
+      <c r="R19" s="18">
+        <v>399.99</v>
+      </c>
+      <c r="S19" s="18">
+        <v>399.99</v>
+      </c>
+      <c r="T19" s="18">
+        <v>164.97</v>
+      </c>
+      <c r="U19" s="18">
+        <v>164.97</v>
+      </c>
+      <c r="V19" s="18">
+        <v>164.97</v>
       </c>
     </row>
   </sheetData>
@@ -12835,7 +13095,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303223D0-B4CB-49AA-99CE-D17D229E45B9}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12847,11 +13107,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF9DD02-7584-4E7B-8430-E8812C31F69E}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
